--- a/files/九龙-旺角-利奥坊．曦岸.xlsx
+++ b/files/九龙-旺角-利奥坊．曦岸.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-05-09</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2020-10-04</t>
+          <t>2020-10-05</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2021-01-31</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-16</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-01-03</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2020-11-29</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2020-09-20</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-10-24</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-01-31</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2020-08-08</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2023-02-22</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2021-07-13</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2021-01-10</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21295,7 +21295,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21853,7 +21853,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-03-20</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2021-01-31</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24271,7 +24271,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2021-04-11</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25077,7 +25077,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25325,7 +25325,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25635,7 +25635,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2020-08-02</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2021-02-20</t>
+          <t>2021-02-21</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25945,7 +25945,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26193,7 +26193,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26255,7 +26255,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2020-05-23</t>
+          <t>2020-05-24</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26317,7 +26317,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2020-08-02</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26379,7 +26379,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26875,7 +26875,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27309,7 +27309,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27371,7 +27371,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27433,7 +27433,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27495,7 +27495,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27743,7 +27743,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27929,7 +27929,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -27991,7 +27991,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28053,7 +28053,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28549,7 +28549,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28859,7 +28859,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-01-23</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29293,7 +29293,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29541,7 +29541,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2021-04-11</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30223,7 +30223,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30347,7 +30347,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2022-11-10</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -30657,7 +30657,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -30719,7 +30719,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -30843,7 +30843,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -30905,7 +30905,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -30967,7 +30967,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31192,7 +31192,7 @@
           <t>A | 381呎 (2房)
 $981万
 $25,739/呎
-(23年-02月-08日)</t>
+(23年-02月-09日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -31200,7 +31200,7 @@
           <t>B | 255呎 (2房)
 $659万
 $25,835/呎
-(23年-02月-27日)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -31208,7 +31208,7 @@
           <t>C | 382呎 (1房)
 $863万
 $22,588/呎
-(23年-12月-28日)</t>
+(23年-12月-29日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -31216,7 +31216,7 @@
           <t>D | 636呎 (3房)
 $1650万
 $25,943/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -31224,7 +31224,7 @@
           <t>E | 555呎 (2房)
 $1590万
 $28,649/呎
-(22年-08月-22日)</t>
+(22年-08月-23日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -31232,7 +31232,7 @@
           <t>F | 397呎 (2房)
 $893万
 $22,492/呎
-(23年-12月-12日)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -31240,7 +31240,7 @@
           <t>G | 524呎 (3房)
 $1513万
 $28,874/呎
-(22年-09月-21日)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr"/>
@@ -31262,7 +31262,7 @@
           <t>A | 256呎 (1房)
 $674万
 $26,338/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -31270,7 +31270,7 @@
           <t>B | 256呎 (1房)
 $676万
 $26,422/呎
-(21年-08月-22日)</t>
+(21年-08月-23日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -31278,7 +31278,7 @@
           <t>C | 256呎 (1房)
 $674万
 $26,322/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -31286,7 +31286,7 @@
           <t>D | 256呎 (1房)
 $674万
 $26,322/呎
-(21年-09月-01日)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -31294,7 +31294,7 @@
           <t>E | 256呎 (1房)
 $676万
 $26,422/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -31302,7 +31302,7 @@
           <t>F | 257呎 (1房)
 $690万
 $26,865/呎
-(21年-07月-29日)</t>
+(21年-07月-30日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -31310,7 +31310,7 @@
           <t>G | 411呎 (2房)
 $827万
 $20,134/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -31318,7 +31318,7 @@
           <t>H | 198呎 (开放式)
 $539万
 $27,219/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -31326,7 +31326,7 @@
           <t>J | 267呎 (1房)
 $724万
 $27,116/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -31334,7 +31334,7 @@
           <t>K | 253呎 (1房)
 $661万
 $26,132/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -31342,7 +31342,7 @@
           <t>L | 255呎 (1房)
 $651万
 $25,511/呎
-(21年-04月-29日)</t>
+(21年-04月-30日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -31350,7 +31350,7 @@
           <t>M | 197呎 (开放式)
 $510万
 $25,899/呎
-(23年-02月-27日)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -31358,7 +31358,7 @@
           <t>N | 193呎 (开放式)
 $528万
 $27,373/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="O6" s="20" t="inlineStr">
@@ -31366,7 +31366,7 @@
           <t>P | 200呎 (开放式)
 $384万
 $19,196/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -31381,7 +31381,7 @@
           <t>A | 256呎 (1房)
 $650万
 $25,376/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -31389,7 +31389,7 @@
           <t>B | 256呎 (1房)
 $672万
 $26,247/呎
-(21年-07月-29日)</t>
+(21年-07月-30日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -31397,7 +31397,7 @@
           <t>C | 256呎 (1房)
 $669万
 $26,147/呎
-(21年-07月-21日)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -31405,7 +31405,7 @@
           <t>D | 256呎 (1房)
 $669万
 $26,147/呎
-(21年-08月-26日)</t>
+(21年-08月-27日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -31413,7 +31413,7 @@
           <t>E | 256呎 (1房)
 $672万
 $26,247/呎
-(21年-07月-27日)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -31421,7 +31421,7 @@
           <t>F | 257呎 (1房)
 $645万
 $25,099/呎
-(20年-12月-30日)</t>
+(20年-12月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -31429,7 +31429,7 @@
           <t>G | 411呎 (2房)
 $811万
 $19,724/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>H | 198呎 (开放式)
 $535万
 $27,037/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -31445,7 +31445,7 @@
           <t>J | 267呎 (1房)
 $727万
 $27,218/呎
-(21年-10月-04日)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -31453,7 +31453,7 @@
           <t>K | 253呎 (1房)
 $678万
 $26,800/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -31461,7 +31461,7 @@
           <t>L | 255呎 (1房)
 $646万
 $25,347/呎
-(21年-05月-09日)</t>
+(21年-05月-10日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -31469,7 +31469,7 @@
           <t>M | 197呎 (开放式)
 $417万
 $21,159/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -31477,7 +31477,7 @@
           <t>N | 193呎 (开放式)
 $525万
 $27,191/呎
-(22年-05月-09日)</t>
+(22年-05月-10日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -31485,7 +31485,7 @@
           <t>P | 200呎 (开放式)
 $381万
 $19,068/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
           <t>A | 256呎 (1房)
 $645万
 $25,207/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -31508,7 +31508,7 @@
           <t>B | 256呎 (1房)
 $667万
 $26,069/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -31516,7 +31516,7 @@
           <t>C | 256呎 (1房)
 $665万
 $25,969/呎
-(21年-07月-21日)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -31524,7 +31524,7 @@
           <t>D | 256呎 (1房)
 $665万
 $25,969/呎
-(21年-08月-23日)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -31532,7 +31532,7 @@
           <t>E | 256呎 (1房)
 $667万
 $26,069/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -31540,7 +31540,7 @@
           <t>F | 257呎 (1房)
 $641万
 $24,933/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -31548,7 +31548,7 @@
           <t>G | 411呎 (2房)
 $805万
 $19,591/呎
-(24年-03月-13日)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -31556,7 +31556,7 @@
           <t>H | 198呎 (开放式)
 $532万
 $26,849/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -31564,7 +31564,7 @@
           <t>J | 267呎 (1房)
 $714万
 $26,760/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -31572,7 +31572,7 @@
           <t>K | 253呎 (1房)
 $667万
 $26,348/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -31580,7 +31580,7 @@
           <t>L | 255呎 (1房)
 $683万
 $26,804/呎
-(21年-03月-24日)</t>
+(21年-03月-25日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -31588,7 +31588,7 @@
           <t>M | 197呎 (开放式)
 $526万
 $26,697/呎
-(22年-08月-03日)</t>
+(22年-08月-04日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -31596,7 +31596,7 @@
           <t>N | 193呎 (开放式)
 $527万
 $27,293/呎
-(21年-11月-08日)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -31604,7 +31604,7 @@
           <t>P | 200呎 (开放式)
 $379万
 $18,944/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -31619,7 +31619,7 @@
           <t>A | 256呎 (1房)
 $641万
 $25,039/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -31627,7 +31627,7 @@
           <t>B | 256呎 (1房)
 $663万
 $25,891/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -31635,7 +31635,7 @@
           <t>C | 256呎 (1房)
 $660万
 $25,791/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -31643,7 +31643,7 @@
           <t>D | 256呎 (1房)
 $660万
 $25,791/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -31651,7 +31651,7 @@
           <t>E | 256呎 (1房)
 $649万
 $25,346/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -31659,7 +31659,7 @@
           <t>F | 257呎 (1房)
 $636万
 $24,766/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -31667,7 +31667,7 @@
           <t>G | 411呎 (2房)
 $800万
 $19,462/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -31675,7 +31675,7 @@
           <t>H | 198呎 (开放式)
 $528万
 $26,672/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -31683,7 +31683,7 @@
           <t>J | 267呎 (1房)
 $710万
 $26,582/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -31691,7 +31691,7 @@
           <t>K | 253呎 (1房)
 $655万
 $25,896/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -31699,7 +31699,7 @@
           <t>L | 255呎 (1房)
 $638万
 $25,015/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -31707,7 +31707,7 @@
           <t>M | 197呎 (开放式)
 $528万
 $26,798/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -31715,7 +31715,7 @@
           <t>N | 193呎 (开放式)
 $518万
 $26,822/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -31723,7 +31723,7 @@
           <t>P | 200呎 (开放式)
 $416万
 $20,786/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -31738,7 +31738,7 @@
           <t>A | 256呎 (1房)
 $637万
 $24,870/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -31746,7 +31746,7 @@
           <t>B | 256呎 (1房)
 $651万
 $25,446/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -31754,7 +31754,7 @@
           <t>C | 256呎 (1房)
 $649万
 $25,347/呎
-(20年-10月-04日)</t>
+(20年-10月-05日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -31762,7 +31762,7 @@
           <t>D | 256呎 (1房)
 $649万
 $25,347/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31770,7 +31770,7 @@
           <t>E | 256呎 (1房)
 $665万
 $25,988/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -31778,7 +31778,7 @@
           <t>F | 258呎 (1房)
 $632万
 $24,501/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -31786,7 +31786,7 @@
           <t>G | 411呎 (2房)
 $794万
 $19,329/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -31794,7 +31794,7 @@
           <t>H | 198呎 (开放式)
 $519万
 $26,211/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -31802,7 +31802,7 @@
           <t>J | 267呎 (1房)
 $705万
 $26,408/呎
-(21年-09月-19日)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -31810,7 +31810,7 @@
           <t>K | 253呎 (1房)
 $651万
 $25,726/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -31818,7 +31818,7 @@
           <t>L | 255呎 (1房)
 $640万
 $25,115/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -31826,7 +31826,7 @@
           <t>M | 197呎 (开放式)
 $519万
 $26,344/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -31834,7 +31834,7 @@
           <t>N | 193呎 (开放式)
 $509万
 $26,359/呎
-(20年-09月-14日)</t>
+(20年-09月-15日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -31842,7 +31842,7 @@
           <t>P | 200呎 (开放式)
 $513万
 $25,668/呎
-(23年-01月-10日)</t>
+(23年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -31857,7 +31857,7 @@
           <t>A | 256呎 (1房)
 $632万
 $24,701/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -31865,7 +31865,7 @@
           <t>B | 256呎 (1房)
 $640万
 $25,001/呎
-(21年-05月-13日)</t>
+(21年-05月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -31873,7 +31873,7 @@
           <t>C | 256呎 (1房)
 $679万
 $26,510/呎
-(20年-06月-11日)</t>
+(20年-06月-12日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -31881,7 +31881,7 @@
           <t>D | 256呎 (1房)
 $679万
 $26,510/呎
-(20年-06月-08日)</t>
+(20年-06月-09日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31889,7 +31889,7 @@
           <t>E | 256呎 (1房)
 $654万
 $25,539/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -31897,7 +31897,7 @@
           <t>F | 257呎 (1房)
 $635万
 $24,692/呎
-(20年-11月-16日)</t>
+(20年-11月-17日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -31905,7 +31905,7 @@
           <t>G | 411呎 (2房)
 $800万
 $19,468/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -31913,7 +31913,7 @@
           <t>H | 198呎 (开放式)
 $510万
 $25,749/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -31921,7 +31921,7 @@
           <t>J | 267呎 (1房)
 $700万
 $26,234/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -31929,7 +31929,7 @@
           <t>K | 253呎 (1房)
 $640万
 $25,283/呎
-(21年-04月-28日)</t>
+(21年-04月-29日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -31937,7 +31937,7 @@
           <t>L | 255呎 (1房)
 $629万
 $24,680/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -31945,7 +31945,7 @@
           <t>M | 197呎 (开放式)
 $521万
 $26,441/呎
-(21年-09月-02日)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -31953,7 +31953,7 @@
           <t>N | 193呎 (开放式)
 $500万
 $25,900/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -31961,7 +31961,7 @@
           <t>P | 200呎 (开放式)
 $516万
 $25,780/呎
-(21年-04月-28日)</t>
+(21年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -31976,7 +31976,7 @@
           <t>A | 256呎 (1房)
 $628万
 $24,532/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -31984,7 +31984,7 @@
           <t>B | 256呎 (1房)
 $642万
 $25,097/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -31992,7 +31992,7 @@
           <t>C | 256呎 (1房)
 $640万
 $24,998/呎
-(20年-10月-29日)</t>
+(20年-10月-30日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -32000,7 +32000,7 @@
           <t>D | 256呎 (1房)
 $633万
 $24,732/呎
-(21年-04月-12日)</t>
+(21年-04月-13日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -32008,7 +32008,7 @@
           <t>E | 256呎 (1房)
 $642万
 $25,097/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -32016,7 +32016,7 @@
           <t>F | 258呎 (1房)
 $626万
 $24,263/呎
-(21年-01月-31日)</t>
+(21年-02月-01日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -32024,7 +32024,7 @@
           <t>G | 410呎 (2房)
 $782万
 $19,068/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -32032,7 +32032,7 @@
           <t>H | 198呎 (开放式)
 $506万
 $25,575/呎
-(21年-05月-13日)</t>
+(21年-05月-14日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -32040,7 +32040,7 @@
           <t>J | 267呎 (1房)
 $689万
 $25,796/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -32048,7 +32048,7 @@
           <t>K | 253呎 (1房)
 $642万
 $25,380/呎
-(21年-01月-21日)</t>
+(21年-01月-22日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -32056,7 +32056,7 @@
           <t>L | 255呎 (1房)
 $665万
 $26,097/呎
-(20年-06月-11日)</t>
+(20年-06月-12日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -32064,7 +32064,7 @@
           <t>M | 197呎 (开放式)
 $512万
 $25,986/呎
-(21年-02月-01日)</t>
+(21年-02月-02日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -32072,7 +32072,7 @@
           <t>N | 193呎 (开放式)
 $496万
 $25,717/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -32080,7 +32080,7 @@
           <t>P | 200呎 (开放式)
 $518万
 $25,878/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -32095,7 +32095,7 @@
           <t>A | 256呎 (1房)
 $624万
 $24,363/呎
-(21年-01月-27日)</t>
+(21年-01月-28日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -32103,7 +32103,7 @@
           <t>B | 256呎 (1房)
 $638万
 $24,925/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -32111,7 +32111,7 @@
           <t>C | 256呎 (1房)
 $629万
 $24,561/呎
-(20年-07月-19日)</t>
+(20年-07月-20日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -32119,7 +32119,7 @@
           <t>D | 256呎 (1房)
 $629万
 $24,561/呎
-(20年-11月-26日)</t>
+(20年-11月-27日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -32127,7 +32127,7 @@
           <t>E | 256呎 (1房)
 $638万
 $24,925/呎
-(20年-09月-27日)</t>
+(20年-09月-28日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -32135,7 +32135,7 @@
           <t>F | 258呎 (1房)
 $622万
 $24,093/呎
-(21年-04月-21日)</t>
+(21年-04月-22日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -32143,7 +32143,7 @@
           <t>G | 410呎 (2房)
 $776万
 $18,936/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -32151,7 +32151,7 @@
           <t>H | 198呎 (开放式)
 $508万
 $25,665/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -32159,7 +32159,7 @@
           <t>J | 267呎 (1房)
 $677万
 $25,358/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -32167,7 +32167,7 @@
           <t>K | 253呎 (1房)
 $638万
 $25,205/呎
-(20年-06月-29日)</t>
+(20年-06月-30日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -32175,7 +32175,7 @@
           <t>L | 255呎 (1房)
 $668万
 $26,184/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -32183,7 +32183,7 @@
           <t>M | 197呎 (开放式)
 $503万
 $25,535/呎
-(20年-09月-15日)</t>
+(20年-09月-16日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -32191,7 +32191,7 @@
           <t>N | 193呎 (开放式)
 $525万
 $27,187/呎
-(20年-10月-15日)</t>
+(20年-10月-16日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -32199,7 +32199,7 @@
           <t>P | 200呎 (开放式)
 $514万
 $25,704/呎
-(20年-09月-02日)</t>
+(20年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -32214,7 +32214,7 @@
           <t>A | 256呎 (1房)
 $619万
 $24,194/呎
-(21年-01月-03日)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -32222,7 +32222,7 @@
           <t>B | 256呎 (1房)
 $633万
 $24,745/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -32230,7 +32230,7 @@
           <t>C | 256呎 (1房)
 $624万
 $24,383/呎
-(21年-04月-15日)</t>
+(21年-04月-16日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -32238,7 +32238,7 @@
           <t>D | 256呎 (1房)
 $631万
 $24,646/呎
-(21年-05月-05日)</t>
+(21年-05月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -32246,7 +32246,7 @@
           <t>E | 256呎 (1房)
 $633万
 $24,745/呎
-(20年-09月-28日)</t>
+(20年-09月-29日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -32254,7 +32254,7 @@
           <t>F | 259呎 (1房)
 $624万
 $24,092/呎
-(21年-01月-25日)</t>
+(21年-01月-26日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -32262,7 +32262,7 @@
           <t>G | 410呎 (2房)
 $782万
 $19,069/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -32270,7 +32270,7 @@
           <t>H | 198呎 (开放式)
 $499万
 $25,213/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -32278,7 +32278,7 @@
           <t>J | 267呎 (1房)
 $666万
 $24,931/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -32286,7 +32286,7 @@
           <t>K | 253呎 (1房)
 $633万
 $25,034/呎
-(20年-10月-18日)</t>
+(20年-10月-19日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -32294,7 +32294,7 @@
           <t>L | 255呎 (1房)
 $663万
 $26,004/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -32302,7 +32302,7 @@
           <t>M | 197呎 (开放式)
 $500万
 $25,355/呎
-(21年-01月-15日)</t>
+(21年-01月-16日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -32310,7 +32310,7 @@
           <t>N | 193呎 (开放式)
 $489万
 $25,361/呎
-(20年-09月-29日)</t>
+(20年-09月-30日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -32318,7 +32318,7 @@
           <t>P | 200呎 (开放式)
 $511万
 $25,530/呎
-(20年-09月-24日)</t>
+(20年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -32333,7 +32333,7 @@
           <t>A | 256呎 (1房)
 $648万
 $25,299/呎
-(20年-12月-01日)</t>
+(20年-12月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -32341,7 +32341,7 @@
           <t>B | 256呎 (1房)
 $622万
 $24,311/呎
-(21年-03月-28日)</t>
+(21年-03月-29日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -32349,7 +32349,7 @@
           <t>C | 256呎 (1房)
 $660万
 $25,775/呎
-(20年-06月-28日)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -32357,7 +32357,7 @@
           <t>D | 256呎 (1房)
 $660万
 $25,775/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -32365,7 +32365,7 @@
           <t>E | 256呎 (1房)
 $629万
 $24,572/呎
-(20年-09月-27日)</t>
+(20年-09月-28日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -32373,7 +32373,7 @@
           <t>F | 259呎 (1房)
 $620万
 $23,928/呎
-(21年-03月-10日)</t>
+(21年-03月-11日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -32381,7 +32381,7 @@
           <t>G | 410呎 (2房)
 $916万
 $22,353/呎
-(23年-09月-28日)</t>
+(23年-09月-29日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -32389,7 +32389,7 @@
           <t>H | 198呎 (开放式)
 $501万
 $25,304/呎
-(21年-04月-27日)</t>
+(21年-04月-28日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -32397,7 +32397,7 @@
           <t>J | 267呎 (1房)
 $654万
 $24,500/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -32405,7 +32405,7 @@
           <t>K | 253呎 (1房)
 $622万
 $24,599/呎
-(20年-09月-23日)</t>
+(20年-09月-24日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -32413,7 +32413,7 @@
           <t>L | 255呎 (1房)
 $619万
 $24,274/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -32421,7 +32421,7 @@
           <t>M | 197呎 (开放式)
 $501万
 $25,456/呎
-(21年-01月-04日)</t>
+(21年-01月-05日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -32429,7 +32429,7 @@
           <t>N | 193呎 (开放式)
 $486万
 $25,182/呎
-(20年-08月-26日)</t>
+(20年-08月-27日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -32437,7 +32437,7 @@
           <t>P | 200呎 (开放式)
 $502万
 $25,082/呎
-(20年-06月-08日)</t>
+(20年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -32452,7 +32452,7 @@
           <t>A | 256呎 (1房)
 $611万
 $23,852/呎
-(21年-01月-21日)</t>
+(21年-01月-22日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -32460,7 +32460,7 @@
           <t>B | 256呎 (1房)
 $625万
 $24,400/呎
-(21年-03月-17日)</t>
+(21年-03月-18日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -32468,7 +32468,7 @@
           <t>C | 256呎 (1房)
 $622万
 $24,300/呎
-(20年-11月-03日)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -32476,7 +32476,7 @@
           <t>D | 256呎 (1房)
 $622万
 $24,300/呎
-(20年-11月-26日)</t>
+(20年-11月-27日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -32484,7 +32484,7 @@
           <t>E | 256呎 (1房)
 $625万
 $24,400/呎
-(20年-07月-21日)</t>
+(20年-07月-22日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -32492,7 +32492,7 @@
           <t>F | 258呎 (1房)
 $648万
 $25,122/呎
-(20年-12月-21日)</t>
+(20年-12月-22日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -32500,7 +32500,7 @@
           <t>G | 410呎 (2房)
 $760万
 $18,541/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -32508,7 +32508,7 @@
           <t>H | 198呎 (开放式)
 $492万
 $24,856/呎
-(21年-04月-18日)</t>
+(21年-04月-19日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -32516,7 +32516,7 @@
           <t>J | 267呎 (1房)
 $650万
 $24,327/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -32524,7 +32524,7 @@
           <t>K | 253呎 (1房)
 $625万
 $24,693/呎
-(20年-07月-20日)</t>
+(20年-07月-21日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -32532,7 +32532,7 @@
           <t>L | 255呎 (1房)
 $615万
 $24,108/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -32540,7 +32540,7 @@
           <t>M | 197呎 (开放式)
 $498万
 $25,275/呎
-(21年-01月-11日)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -32548,7 +32548,7 @@
           <t>N | 193呎 (开放式)
 $488万
 $25,273/呎
-(20年-09月-21日)</t>
+(20年-09月-22日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -32556,7 +32556,7 @@
           <t>P | 200呎 (开放式)
 $504万
 $25,178/呎
-(20年-05月-26日)</t>
+(20年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -32571,7 +32571,7 @@
           <t>A | 256呎 (1房)
 $606万
 $23,684/呎
-(20年-12月-14日)</t>
+(20年-12月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -32579,7 +32579,7 @@
           <t>B | 256呎 (1房)
 $620万
 $24,223/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -32587,7 +32587,7 @@
           <t>C | 256呎 (1房)
 $618万
 $24,124/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -32595,7 +32595,7 @@
           <t>D | 256呎 (1房)
 $611万
 $23,868/呎
-(20年-10月-21日)</t>
+(20年-10月-22日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -32603,7 +32603,7 @@
           <t>E | 256呎 (1房)
 $614万
 $23,966/呎
-(20年-09月-20日)</t>
+(20年-09月-21日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -32611,7 +32611,7 @@
           <t>F | 258呎 (1房)
 $611万
 $23,682/呎
-(20年-11月-29日)</t>
+(20年-11月-30日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -32619,7 +32619,7 @@
           <t>G | 411呎 (2房)
 $999万
 $24,314/呎
-(21年-04月-28日)</t>
+(21年-04月-29日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -32627,7 +32627,7 @@
           <t>H | 198呎 (开放式)
 $487万
 $24,589/呎
-(21年-04月-18日)</t>
+(21年-04月-19日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -32635,7 +32635,7 @@
           <t>J | 267呎 (1房)
 $643万
 $24,074/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -32643,7 +32643,7 @@
           <t>K | 253呎 (1房)
 $614万
 $24,257/呎
-(20年-06月-28日)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -32651,7 +32651,7 @@
           <t>L | 255呎 (1房)
 $610万
 $23,939/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -32659,7 +32659,7 @@
           <t>M | 197呎 (开放式)
 $500万
 $25,365/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -32667,7 +32667,7 @@
           <t>N | 193呎 (开放式)
 $484万
 $25,088/呎
-(20年-09月-06日)</t>
+(20年-09月-07日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -32675,7 +32675,7 @@
           <t>P | 200呎 (开放式)
 $500万
 $25,004/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -32690,7 +32690,7 @@
           <t>A | 256呎 (1房)
 $596万
 $23,265/呎
-(20年-12月-10日)</t>
+(20年-12月-11日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -32698,7 +32698,7 @@
           <t>B | 256呎 (1房)
 $609万
 $23,791/呎
-(20年-09月-29日)</t>
+(20年-09月-30日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -32706,7 +32706,7 @@
           <t>C | 256呎 (1房)
 $613万
 $23,948/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -32714,7 +32714,7 @@
           <t>D | 256呎 (1房)
 $613万
 $23,948/呎
-(20年-07月-27日)</t>
+(20年-07月-28日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -32722,7 +32722,7 @@
           <t>E | 256呎 (1房)
 $609万
 $23,791/呎
-(20年-07月-29日)</t>
+(20年-07月-30日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -32730,7 +32730,7 @@
           <t>F | 259呎 (1房)
 $639万
 $24,670/呎
-(20年-10月-25日)</t>
+(20年-10月-26日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -32738,7 +32738,7 @@
           <t>G | 411呎 (2房)
 $897万
 $21,829/呎
-(23年-09月-06日)</t>
+(23年-09月-07日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -32746,7 +32746,7 @@
           <t>H | 198呎 (开放式)
 $487万
 $24,582/呎
-(21年-03月-22日)</t>
+(21年-03月-23日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -32754,7 +32754,7 @@
           <t>J | 267呎 (1房)
 $636万
 $23,820/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -32762,7 +32762,7 @@
           <t>K | 253呎 (1房)
 $616万
 $24,347/呎
-(20年-06月-12日)</t>
+(20年-06月-13日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -32770,7 +32770,7 @@
           <t>L | 255呎 (1房)
 $638万
 $25,037/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -32778,7 +32778,7 @@
           <t>M | 197呎 (开放式)
 $486万
 $24,657/呎
-(20年-09月-02日)</t>
+(20年-09月-03日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -32786,7 +32786,7 @@
           <t>N | 193呎 (开放式)
 $476万
 $24,643/呎
-(20年-09月-07日)</t>
+(20年-09月-08日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -32794,7 +32794,7 @@
           <t>P | 200呎 (开放式)
 $491万
 $24,566/呎
-(20年-06月-04日)</t>
+(20年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -32809,7 +32809,7 @@
           <t>A | 256呎 (1房)
 $591万
 $23,094/呎
-(20年-11月-19日)</t>
+(20年-11月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -32817,7 +32817,7 @@
           <t>B | 256呎 (1房)
 $611万
 $23,875/呎
-(20年-09月-14日)</t>
+(20年-09月-15日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -32825,7 +32825,7 @@
           <t>C | 256呎 (1房)
 $609万
 $23,775/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -32833,7 +32833,7 @@
           <t>D | 256呎 (1房)
 $609万
 $23,775/呎
-(20年-07月-27日)</t>
+(20年-07月-28日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -32841,7 +32841,7 @@
           <t>E | 256呎 (1房)
 $611万
 $23,875/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -32849,7 +32849,7 @@
           <t>F | 259呎 (1房)
 $596万
 $23,009/呎
-(20年-11月-18日)</t>
+(20年-11月-19日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -32857,7 +32857,7 @@
           <t>G | 411呎 (2房)
 $985万
 $23,967/呎
-(21年-03月-04日)</t>
+(21年-03月-05日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -32865,7 +32865,7 @@
           <t>H | 198呎 (开放式)
 $480万
 $24,222/呎
-(21年-01月-07日)</t>
+(21年-01月-08日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -32873,7 +32873,7 @@
           <t>J | 267呎 (1房)
 $627万
 $23,479/呎
-(21年-03月-24日)</t>
+(21年-03月-25日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -32881,7 +32881,7 @@
           <t>K | 253呎 (1房)
 $612万
 $24,172/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -32889,7 +32889,7 @@
           <t>L | 255呎 (1房)
 $602万
 $23,607/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -32897,7 +32897,7 @@
           <t>M | 197呎 (开放式)
 $487万
 $24,741/呎
-(20年-09月-02日)</t>
+(20年-09月-03日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -32905,7 +32905,7 @@
           <t>N | 193呎 (开放式)
 $472万
 $24,464/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -32913,7 +32913,7 @@
           <t>P | 200呎 (开放式)
 $493万
 $24,656/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32928,7 @@
           <t>A | 256呎 (1房)
 $587万
 $22,927/呎
-(20年-10月-23日)</t>
+(20年-10月-24日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -32936,7 +32936,7 @@
           <t>B | 256呎 (1房)
 $607万
 $23,698/呎
-(20年-09月-08日)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -32944,7 +32944,7 @@
           <t>C | 256呎 (1房)
 $598万
 $23,348/呎
-(20年-06月-09日)</t>
+(20年-06月-10日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -32952,7 +32952,7 @@
           <t>D | 256呎 (1房)
 $598万
 $23,348/呎
-(20年-06月-04日)</t>
+(20年-06月-05日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -32960,7 +32960,7 @@
           <t>E | 256呎 (1房)
 $639万
 $24,959/呎
-(20年-07月-19日)</t>
+(20年-07月-20日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -32968,7 +32968,7 @@
           <t>F | 259呎 (1房)
 $598万
 $23,090/呎
-(20年-11月-16日)</t>
+(20年-11月-17日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -32976,7 +32976,7 @@
           <t>G | 410呎 (2房)
 $999万
 $24,358/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -32984,7 +32984,7 @@
           <t>H | 198呎 (开放式)
 $471万
 $23,781/呎
-(20年-12月-20日)</t>
+(20年-12月-21日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -32992,7 +32992,7 @@
           <t>J | 267呎 (1房)
 $616万
 $23,065/呎
-(21年-04月-20日)</t>
+(21年-04月-21日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -33000,7 +33000,7 @@
           <t>K | 253呎 (1房)
 $607万
 $24,002/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -33008,7 +33008,7 @@
           <t>L | 255呎 (1房)
 $598万
 $23,441/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -33016,7 +33016,7 @@
           <t>M | 197呎 (开放式)
 $515万
 $26,137/呎
-(20年-08月-20日)</t>
+(20年-08月-21日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -33024,7 +33024,7 @@
           <t>N | 193呎 (开放式)
 $469万
 $24,286/呎
-(20年-08月-25日)</t>
+(20年-08月-26日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -33032,7 +33032,7 @@
           <t>P | 200呎 (开放式)
 $490万
 $24,478/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
           <t>A | 256呎 (1房)
 $585万
 $22,847/呎
-(20年-12月-14日)</t>
+(20年-12月-15日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -33055,7 +33055,7 @@
           <t>B | 256呎 (1房)
 $605万
 $23,614/呎
-(20年-08月-26日)</t>
+(20年-08月-27日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -33063,7 +33063,7 @@
           <t>C | 256呎 (1房)
 $596万
 $23,265/呎
-(20年-05月-28日)</t>
+(20年-05月-29日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -33071,7 +33071,7 @@
           <t>D | 256呎 (1房)
 $602万
 $23,515/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -33079,7 +33079,7 @@
           <t>E | 256呎 (1房)
 $598万
 $23,363/呎
-(20年-06月-15日)</t>
+(20年-06月-16日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -33087,7 +33087,7 @@
           <t>F | 258呎 (1房)
 $590万
 $22,850/呎
-(20年-12月-07日)</t>
+(20年-12月-08日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -33095,7 +33095,7 @@
           <t>G | 411呎 (2房)
 $974万
 $23,706/呎
-(21年-04月-22日)</t>
+(21年-04月-23日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -33103,7 +33103,7 @@
           <t>H | 198呎 (开放式)
 $474万
 $23,951/呎
-(21年-01月-31日)</t>
+(21年-02月-01日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -33111,7 +33111,7 @@
           <t>J | 267呎 (1房)
 $614万
 $22,978/呎
-(21年-05月-17日)</t>
+(21年-05月-18日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -33119,7 +33119,7 @@
           <t>K | 253呎 (1房)
 $599万
 $23,662/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -33127,7 +33127,7 @@
           <t>L | 255呎 (1房)
 $595万
 $23,353/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -33135,7 +33135,7 @@
           <t>M | 197呎 (开放式)
 $482万
 $24,478/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -33143,7 +33143,7 @@
           <t>N | 193呎 (开放式)
 $472万
 $24,455/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -33151,7 +33151,7 @@
           <t>P | 200呎 (开放式)
 $483万
 $24,134/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33166,7 +33166,7 @@
           <t>A | 256呎 (1房)
 $618万
 $24,139/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -33174,7 +33174,7 @@
           <t>B | 256呎 (1房)
 $600万
 $23,438/呎
-(20年-08月-26日)</t>
+(20年-08月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -33182,7 +33182,7 @@
           <t>C | 256呎 (1房)
 $591万
 $23,090/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -33190,7 +33190,7 @@
           <t>D | 256呎 (1房)
 $597万
 $23,338/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -33198,7 +33198,7 @@
           <t>E | 256呎 (1房)
 $594万
 $23,188/呎
-(20年-07月-21日)</t>
+(20年-07月-22日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -33206,7 +33206,7 @@
           <t>F | 259呎 (1房)
 $585万
 $22,596/呎
-(20年-11月-26日)</t>
+(20年-11月-27日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -33214,7 +33214,7 @@
           <t>G | 411呎 (2房)
 $977万
 $23,782/呎
-(21年-07月-06日)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -33222,7 +33222,7 @@
           <t>H | 198呎 (开放式)
 $496万
 $25,030/呎
-(20年-11月-17日)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -33230,7 +33230,7 @@
           <t>J | 267呎 (1房)
 $635万
 $23,771/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -33238,7 +33238,7 @@
           <t>K | 253呎 (1房)
 $633万
 $25,004/呎
-(20年-06月-28日)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -33246,7 +33246,7 @@
           <t>L | 255呎 (1房)
 $591万
 $23,187/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -33254,7 +33254,7 @@
           <t>M | 197呎 (开放式)
 $479万
 $24,302/呎
-(20年-08月-25日)</t>
+(20年-08月-26日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -33262,7 +33262,7 @@
           <t>N | 193呎 (开放式)
 $468万
 $24,274/呎
-(20年-08月-08日)</t>
+(20年-08月-09日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -33270,7 +33270,7 @@
           <t>P | 200呎 (开放式)
 $515万
 $25,760/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33285,7 +33285,7 @@
           <t>A | 256呎 (1房)
 $580万
 $22,670/呎
-(20年-11月-30日)</t>
+(20年-12月-01日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -33293,7 +33293,7 @@
           <t>B | 256呎 (1房)
 $593万
 $23,173/呎
-(20年-09月-08日)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -33301,7 +33301,7 @@
           <t>C | 256呎 (1房)
 $622万
 $24,301/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -33309,7 +33309,7 @@
           <t>D | 256呎 (1房)
 $591万
 $23,074/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -33317,7 +33317,7 @@
           <t>E | 256呎 (1房)
 $587万
 $22,927/呎
-(20年-07月-09日)</t>
+(20年-07月-10日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -33325,7 +33325,7 @@
           <t>F | 258呎 (1房)
 $579万
 $22,432/呎
-(20年-11月-09日)</t>
+(20年-11月-10日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -33333,7 +33333,7 @@
           <t>G | 411呎 (2房)
 $977万
 $23,766/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -33341,7 +33341,7 @@
           <t>H | 198呎 (开放式)
 $465万
 $23,495/呎
-(21年-01月-11日)</t>
+(21年-01月-12日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -33349,7 +33349,7 @@
           <t>J | 267呎 (1房)
 $628万
 $23,511/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -33357,7 +33357,7 @@
           <t>K | 253呎 (1房)
 $626万
 $24,734/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -33365,7 +33365,7 @@
           <t>L | 255呎 (1房)
 $585万
 $22,936/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -33373,7 +33373,7 @@
           <t>M | 197呎 (开放式)
 $373万
 $18,920/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -33381,7 +33381,7 @@
           <t>N | 193呎 (开放式)
 $458万
 $23,746/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -33389,7 +33389,7 @@
           <t>P | 200呎 (开放式)
 $479万
 $23,951/呎
-(20年-06月-10日)</t>
+(20年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33404,7 +33404,7 @@
           <t>A | 235呎 (1房)
 $500万
 $21,277/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -33412,7 +33412,7 @@
           <t>B | 235呎 (1房)
 $620万
 $26,383/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -33420,7 +33420,7 @@
           <t>C | 235呎 (1房)
 $610万
 $25,957/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -33428,7 +33428,7 @@
           <t>D | 235呎 (1房)
 $625万
 $26,596/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -33436,7 +33436,7 @@
           <t>E | 235呎 (1房)
 $520万
 $22,128/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -33444,7 +33444,7 @@
           <t>F | 237呎 (1房)
 $550万
 $23,207/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -33452,7 +33452,7 @@
           <t>G | 374呎 (2房)
 $975万
 $26,070/呎
-(23年-02月-05日)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -33460,7 +33460,7 @@
           <t>H | 178呎 (开放式)
 $380万
 $21,348/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -33468,7 +33468,7 @@
           <t>J | 243呎 (1房)
 $580万
 $23,868/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -33476,7 +33476,7 @@
           <t>K | 231呎 (1房)
 $640万
 $27,706/呎
-(22年-09月-27日)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -33484,7 +33484,7 @@
           <t>L | 234呎 (1房)
 $560万
 $23,932/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -33492,7 +33492,7 @@
           <t>M | 174呎 (开放式)
 $415万
 $23,851/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -33500,7 +33500,7 @@
           <t>N | 171呎 (开放式)
 $485万
 $28,363/呎
-(22年-10月-16日)</t>
+(22年-10月-17日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -33508,7 +33508,7 @@
           <t>P | 179呎 (开放式)
 $420万
 $23,464/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -33696,7 +33696,7 @@
           <t>B | 383呎 (1房)
 $1086万
 $28,368/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33704,7 +33704,7 @@
           <t>C | 260呎 (2房)
 $739万
 $28,426/呎
-(23年-03月-05日)</t>
+(23年-03月-06日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33712,7 +33712,7 @@
           <t>D | 657呎 (3房)
 $1895万
 $28,843/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -33720,7 +33720,7 @@
           <t>E | 321呎 (1房)
 $800万
 $24,922/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -33728,7 +33728,7 @@
           <t>F | 267呎 (1房)
 $698万
 $26,134/呎
-(23年-02月-22日)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -33748,7 +33748,7 @@
           <t>A | 259呎 (1房)
 $688万
 $26,549/呎
-(21年-07月-13日)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -33756,7 +33756,7 @@
           <t>B | 413呎 (2房)
 $1172万
 $28,379/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -33764,7 +33764,7 @@
           <t>C | 248呎 (1房)
 $678万
 $27,355/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -33772,7 +33772,7 @@
           <t>D | 257呎 (1房)
 $695万
 $27,032/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -33780,7 +33780,7 @@
           <t>E | 257呎 (1房)
 $711万
 $27,657/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -33788,7 +33788,7 @@
           <t>F | 257呎 (1房)
 $689万
 $26,825/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -33796,7 +33796,7 @@
           <t>G | 399呎 (2房)
 $1070万
 $26,807/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -33804,7 +33804,7 @@
           <t>H | 286呎 (1房)
 $776万
 $27,145/呎
-(21年-12月-22日)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -33812,7 +33812,7 @@
           <t>J | 193呎 (开放式)
 $420万
 $21,763/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -33820,7 +33820,7 @@
           <t>K | 194呎 (开放式)
 $389万
 $20,049/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -33828,7 +33828,7 @@
           <t>L | 197呎 (开放式)
 $421万
 $21,388/呎
-(24年-06月-10日)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -33843,7 +33843,7 @@
           <t>A | 258呎 (1房)
 $676万
 $26,213/呎
-(21年-07月-04日)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -33851,7 +33851,7 @@
           <t>B | 413呎 (2房)
 $1152万
 $27,900/呎
-(21年-08月-12日)</t>
+(21年-08月-13日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -33859,7 +33859,7 @@
           <t>C | 248呎 (1房)
 $667万
 $26,880/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -33867,7 +33867,7 @@
           <t>D | 257呎 (1房)
 $698万
 $27,150/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -33875,7 +33875,7 @@
           <t>E | 257呎 (1房)
 $706万
 $27,480/呎
-(21年-08月-11日)</t>
+(21年-08月-12日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -33883,7 +33883,7 @@
           <t>F | 257呎 (1房)
 $678万
 $26,369/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -33891,7 +33891,7 @@
           <t>G | 399呎 (2房)
 $1063万
 $26,633/呎
-(21年-08月-30日)</t>
+(21年-08月-31日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -33899,7 +33899,7 @@
           <t>H | 286呎 (1房)
 $633万
 $22,137/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -33907,7 +33907,7 @@
           <t>J | 193呎 (开放式)
 $417万
 $21,617/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -33915,7 +33915,7 @@
           <t>K | 194呎 (开放式)
 $381万
 $19,623/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -33923,7 +33923,7 @@
           <t>L | 197呎 (开放式)
 $419万
 $21,249/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -33938,7 +33938,7 @@
           <t>A | 259呎 (1房)
 $658万
 $25,402/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -33946,7 +33946,7 @@
           <t>B | 413呎 (2房)
 $1157万
 $28,007/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -33954,7 +33954,7 @@
           <t>C | 248呎 (1房)
 $669万
 $26,991/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -33962,7 +33962,7 @@
           <t>D | 257呎 (1房)
 $693万
 $26,975/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -33970,7 +33970,7 @@
           <t>E | 257呎 (1房)
 $709万
 $27,590/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -33978,7 +33978,7 @@
           <t>F | 257呎 (1房)
 $673万
 $26,196/呎
-(21年-05月-12日)</t>
+(21年-05月-13日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -33986,7 +33986,7 @@
           <t>G | 399呎 (2房)
 $1056万
 $26,460/呎
-(21年-08月-30日)</t>
+(21年-08月-31日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -33994,7 +33994,7 @@
           <t>H | 286呎 (1房)
 $750万
 $26,222/呎
-(22年-08月-15日)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -34002,7 +34002,7 @@
           <t>J | 193呎 (开放式)
 $375万
 $19,444/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -34010,7 +34010,7 @@
           <t>K | 194呎 (开放式)
 $508万
 $26,179/呎
-(23年-03月-09日)</t>
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -34018,7 +34018,7 @@
           <t>L | 197呎 (开放式)
 $506万
 $25,675/呎
-(23年-03月-15日)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -34033,7 +34033,7 @@
           <t>A | 259呎 (1房)
 $661万
 $25,503/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34041,7 +34041,7 @@
           <t>B | 413呎 (2房)
 $1096万
 $26,529/呎
-(21年-01月-10日)</t>
+(21年-01月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34049,7 +34049,7 @@
           <t>C | 247呎 (1房)
 $653万
 $26,454/呎
-(21年-04月-22日)</t>
+(21年-04月-23日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34057,7 +34057,7 @@
           <t>D | 257呎 (1房)
 $677万
 $26,340/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34065,7 +34065,7 @@
           <t>E | 257呎 (1房)
 $692万
 $26,944/呎
-(21年-08月-04日)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34073,7 +34073,7 @@
           <t>F | 257呎 (1房)
 $660万
 $25,700/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34081,7 +34081,7 @@
           <t>G | 399呎 (2房)
 $1000万
 $25,059/呎
-(21年-06月-08日)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34089,7 +34089,7 @@
           <t>H | 286呎 (1房)
 $625万
 $21,843/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -34097,7 +34097,7 @@
           <t>J | 193呎 (开放式)
 $528万
 $27,378/呎
-(22年-05月-11日)</t>
+(22年-05月-12日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -34105,7 +34105,7 @@
           <t>K | 194呎 (开放式)
 $533万
 $27,452/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -34113,7 +34113,7 @@
           <t>L | 197呎 (开放式)
 $530万
 $26,923/呎
-(21年-12月-19日)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -34128,7 +34128,7 @@
           <t>A | 258呎 (1房)
 $649万
 $25,165/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -34136,7 +34136,7 @@
           <t>B | 413呎 (2房)
 $1114万
 $26,984/呎
-(22年-05月-11日)</t>
+(22年-05月-12日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -34144,7 +34144,7 @@
           <t>C | 247呎 (1房)
 $645万
 $26,096/呎
-(21年-04月-15日)</t>
+(21年-04月-16日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -34152,7 +34152,7 @@
           <t>D | 257呎 (1房)
 $672万
 $26,166/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34160,7 +34160,7 @@
           <t>E | 257呎 (1房)
 $683万
 $26,589/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34168,7 +34168,7 @@
           <t>F | 257呎 (1房)
 $659万
 $25,632/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34176,7 +34176,7 @@
           <t>G | 399呎 (2房)
 $997万
 $24,991/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34184,7 +34184,7 @@
           <t>H | 287呎 (1房)
 $764万
 $26,606/呎
-(22年-05月-04日)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -34192,7 +34192,7 @@
           <t>J | 193呎 (开放式)
 $514万
 $26,618/呎
-(22年-09月-15日)</t>
+(22年-09月-16日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -34200,7 +34200,7 @@
           <t>K | 194呎 (开放式)
 $534万
 $27,548/呎
-(21年-09月-08日)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -34208,7 +34208,7 @@
           <t>L | 197呎 (开放式)
 $527万
 $26,745/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -34223,7 +34223,7 @@
           <t>A | 258呎 (1房)
 $638万
 $24,735/呎
-(21年-05月-01日)</t>
+(21年-05月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -34231,7 +34231,7 @@
           <t>B | 413呎 (2房)
 $1107万
 $26,802/呎
-(22年-03月-19日)</t>
+(22年-03月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -34239,7 +34239,7 @@
           <t>C | 247呎 (1房)
 $647万
 $26,194/呎
-(21年-04月-22日)</t>
+(21年-04月-23日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -34247,7 +34247,7 @@
           <t>D | 257呎 (1房)
 $661万
 $25,718/呎
-(21年-04月-29日)</t>
+(21年-04月-30日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -34255,7 +34255,7 @@
           <t>E | 257呎 (1房)
 $679万
 $26,415/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -34263,7 +34263,7 @@
           <t>F | 257呎 (1房)
 $647万
 $25,193/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -34271,7 +34271,7 @@
           <t>G | 400呎 (2房)
 $990万
 $24,762/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -34279,7 +34279,7 @@
           <t>H | 286呎 (1房)
 $750万
 $26,238/呎
-(22年-04月-26日)</t>
+(22年-04月-27日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -34287,7 +34287,7 @@
           <t>J | 193呎 (开放式)
 $527万
 $27,293/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -34295,7 +34295,7 @@
           <t>K | 193呎 (开放式)
 $525万
 $27,220/呎
-(21年-08月-23日)</t>
+(21年-08月-24日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -34303,7 +34303,7 @@
           <t>L | 197呎 (开放式)
 $529万
 $26,841/呎
-(21年-08月-29日)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
     </row>
@@ -34318,7 +34318,7 @@
           <t>A | 258呎 (1房)
 $641万
 $24,833/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -34326,7 +34326,7 @@
           <t>B | 413呎 (2房)
 $1099万
 $26,618/呎
-(22年-06月-01日)</t>
+(22年-06月-02日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -34334,7 +34334,7 @@
           <t>C | 248呎 (1房)
 $636万
 $25,635/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -34342,7 +34342,7 @@
           <t>D | 257呎 (1房)
 $664万
 $25,823/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -34350,7 +34350,7 @@
           <t>E | 257呎 (1房)
 $661万
 $25,702/呎
-(20年-07月-16日)</t>
+(20年-07月-17日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -34358,7 +34358,7 @@
           <t>F | 257呎 (1房)
 $650万
 $25,289/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -34366,7 +34366,7 @@
           <t>G | 400呎 (2房)
 $984万
 $24,593/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -34374,7 +34374,7 @@
           <t>H | 287呎 (1房)
 $745万
 $25,968/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -34382,7 +34382,7 @@
           <t>J | 193呎 (开放式)
 $518万
 $26,822/呎
-(21年-09月-13日)</t>
+(21年-09月-14日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -34390,7 +34390,7 @@
           <t>K | 193呎 (开放式)
 $522万
 $27,033/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -34398,7 +34398,7 @@
           <t>L | 197呎 (开放式)
 $514万
 $26,105/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -34413,7 +34413,7 @@
           <t>A | 258呎 (1房)
 $636万
 $24,662/呎
-(21年-05月-06日)</t>
+(21年-05月-07日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -34421,7 +34421,7 @@
           <t>B | 413呎 (2房)
 $1103万
 $26,715/呎
-(22年-06月-20日)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -34429,7 +34429,7 @@
           <t>C | 248呎 (1房)
 $631万
 $25,459/呎
-(21年-01月-31日)</t>
+(21年-02月-01日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -34437,7 +34437,7 @@
           <t>D | 257呎 (1房)
 $652万
 $25,374/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -34445,7 +34445,7 @@
           <t>E | 257呎 (1房)
 $649万
 $25,255/呎
-(20年-12月-23日)</t>
+(20年-12月-24日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -34453,7 +34453,7 @@
           <t>F | 257呎 (1房)
 $646万
 $25,120/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -34461,7 +34461,7 @@
           <t>G | 399呎 (2房)
 $967万
 $24,227/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -34469,7 +34469,7 @@
           <t>H | 287呎 (1房)
 $740万
 $25,786/呎
-(21年-10月-14日)</t>
+(21年-10月-15日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -34477,7 +34477,7 @@
           <t>J | 193呎 (开放式)
 $514万
 $26,630/呎
-(21年-07月-21日)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -34485,7 +34485,7 @@
           <t>K | 194呎 (开放式)
 $513万
 $26,427/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -34493,7 +34493,7 @@
           <t>L | 197呎 (开放式)
 $511万
 $25,929/呎
-(20年-10月-18日)</t>
+(20年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -34508,7 +34508,7 @@
           <t>A | 258呎 (1房)
 $625万
 $24,234/呎
-(21年-05月-04日)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -34516,7 +34516,7 @@
           <t>B | 413呎 (2房)
 $1084万
 $26,253/呎
-(22年-07月-25日)</t>
+(22年-07月-26日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -34524,7 +34524,7 @@
           <t>C | 248呎 (1房)
 $634万
 $25,547/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -34532,7 +34532,7 @@
           <t>D | 257呎 (1房)
 $698万
 $27,163/呎
-(21年-04月-25日)</t>
+(21年-04月-26日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -34540,7 +34540,7 @@
           <t>E | 257呎 (1房)
 $652万
 $25,354/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -34548,7 +34548,7 @@
           <t>F | 257呎 (1房)
 $641万
 $24,948/呎
-(21年-03月-17日)</t>
+(21年-03月-18日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -34556,7 +34556,7 @@
           <t>G | 400呎 (2房)
 $970万
 $24,257/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -34564,7 +34564,7 @@
           <t>H | 286呎 (1房)
 $709万
 $24,785/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -34572,7 +34572,7 @@
           <t>J | 193呎 (开放式)
 $505万
 $26,169/呎
-(21年-03月-22日)</t>
+(21年-03月-23日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -34580,7 +34580,7 @@
           <t>K | 194呎 (开放式)
 $509万
 $26,242/呎
-(20年-11月-10日)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -34588,7 +34588,7 @@
           <t>L | 197呎 (开放式)
 $513万
 $26,021/呎
-(21年-08月-30日)</t>
+(21年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -34603,7 +34603,7 @@
           <t>A | 259呎 (1房)
 $621万
 $23,975/呎
-(21年-05月-19日)</t>
+(21年-05月-20日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -34611,7 +34611,7 @@
           <t>B | 413呎 (2房)
 $1044万
 $25,287/呎
-(20年-06月-28日)</t>
+(20年-06月-29日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -34619,7 +34619,7 @@
           <t>C | 248呎 (1房)
 $622万
 $25,099/呎
-(20年-12月-29日)</t>
+(20年-12月-30日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -34627,7 +34627,7 @@
           <t>D | 257呎 (1房)
 $652万
 $25,362/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -34635,7 +34635,7 @@
           <t>E | 257呎 (1房)
 $647万
 $25,179/呎
-(20年-10月-15日)</t>
+(20年-10月-16日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -34643,7 +34643,7 @@
           <t>F | 257呎 (1房)
 $637万
 $24,776/呎
-(21年-04月-11日)</t>
+(21年-04月-12日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -34651,7 +34651,7 @@
           <t>G | 400呎 (2房)
 $964万
 $24,088/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -34659,7 +34659,7 @@
           <t>H | 287呎 (1房)
 $733万
 $25,551/呎
-(21年-09月-17日)</t>
+(21年-09月-18日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -34667,7 +34667,7 @@
           <t>J | 193呎 (开放式)
 $501万
 $25,984/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -34675,7 +34675,7 @@
           <t>K | 194呎 (开放式)
 $516万
 $26,613/呎
-(21年-06月-29日)</t>
+(21年-06月-30日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -34683,7 +34683,7 @@
           <t>L | 197呎 (开放式)
 $504万
 $25,576/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -34698,7 +34698,7 @@
           <t>A | 258呎 (1房)
 $623万
 $24,159/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -34706,7 +34706,7 @@
           <t>B | 413呎 (2房)
 $1047万
 $25,342/呎
-(22年-08月-15日)</t>
+(22年-08月-16日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -34714,7 +34714,7 @@
           <t>C | 248呎 (1房)
 $625万
 $25,190/呎
-(20年-10月-29日)</t>
+(20年-10月-30日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -34722,7 +34722,7 @@
           <t>D | 257呎 (1房)
 $649万
 $25,248/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -34730,7 +34730,7 @@
           <t>E | 257呎 (1房)
 $643万
 $25,007/呎
-(20年-12月-07日)</t>
+(20年-12月-08日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -34738,7 +34738,7 @@
           <t>F | 257呎 (1房)
 $632万
 $24,605/呎
-(21年-03月-17日)</t>
+(21年-03月-18日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -34746,7 +34746,7 @@
           <t>G | 400呎 (2房)
 $957万
 $23,921/呎
-(21年-03月-29日)</t>
+(21年-03月-30日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -34754,7 +34754,7 @@
           <t>H | 287呎 (1房)
 $725万
 $25,246/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -34762,7 +34762,7 @@
           <t>J | 193呎 (开放式)
 $498万
 $25,794/呎
-(20年-08月-12日)</t>
+(20年-08月-13日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -34770,7 +34770,7 @@
           <t>K | 194呎 (开放式)
 $502万
 $25,874/呎
-(21年-03月-23日)</t>
+(21年-03月-24日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -34778,7 +34778,7 @@
           <t>L | 197呎 (开放式)
 $495万
 $25,124/呎
-(21年-06月-03日)</t>
+(21年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -34793,7 +34793,7 @@
           <t>A | 258呎 (1房)
 $619万
 $23,988/呎
-(21年-05月-12日)</t>
+(21年-05月-13日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -34801,7 +34801,7 @@
           <t>B | 413呎 (2房)
 $1021万
 $24,715/呎
-(22年-10月-10日)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -34809,7 +34809,7 @@
           <t>C | 248呎 (1房)
 $648万
 $26,147/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -34817,7 +34817,7 @@
           <t>D | 257呎 (1房)
 $633万
 $24,632/呎
-(21年-05月-12日)</t>
+(21年-05月-13日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -34825,7 +34825,7 @@
           <t>E | 257呎 (1房)
 $657万
 $25,546/呎
-(21年-08月-26日)</t>
+(21年-08月-27日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -34833,7 +34833,7 @@
           <t>F | 257呎 (1房)
 $617万
 $24,006/呎
-(21年-02月-20日)</t>
+(21年-02月-21日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -34841,7 +34841,7 @@
           <t>G | 399呎 (2房)
 $953万
 $23,895/呎
-(21年-06月-22日)</t>
+(21年-06月-23日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -34849,7 +34849,7 @@
           <t>H | 287呎 (1房)
 $717万
 $24,975/呎
-(21年-09月-08日)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -34857,7 +34857,7 @@
           <t>J | 193呎 (开放式)
 $519万
 $26,874/呎
-(20年-07月-29日)</t>
+(20年-07月-30日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -34865,7 +34865,7 @@
           <t>K | 194呎 (开放式)
 $497万
 $25,598/呎
-(20年-08月-02日)</t>
+(20年-08月-03日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -34873,7 +34873,7 @@
           <t>L | 197呎 (开放式)
 $521万
 $26,464/呎
-(20年-06月-15日)</t>
+(20年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -34888,7 +34888,7 @@
           <t>A | 258呎 (1房)
 $615万
 $23,821/呎
-(21年-04月-13日)</t>
+(21年-04月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -34896,7 +34896,7 @@
           <t>B | 413呎 (2房)
 $1006万
 $24,359/呎
-(22年-10月-20日)</t>
+(22年-10月-21日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -34904,7 +34904,7 @@
           <t>C | 248呎 (1房)
 $646万
 $26,028/呎
-(20年-10月-07日)</t>
+(20年-10月-08日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -34912,7 +34912,7 @@
           <t>D | 257呎 (1房)
 $624万
 $24,285/呎
-(21年-05月-14日)</t>
+(21年-05月-15日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -34920,7 +34920,7 @@
           <t>E | 257呎 (1房)
 $665万
 $25,864/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -34928,7 +34928,7 @@
           <t>F | 257呎 (1房)
 $608万
 $23,666/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -34936,7 +34936,7 @@
           <t>G | 400呎 (2房)
 $920万
 $23,001/呎
-(21年-06月-21日)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -34944,7 +34944,7 @@
           <t>H | 287呎 (1房)
 $684万
 $23,827/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -34952,7 +34952,7 @@
           <t>J | 193呎 (开放式)
 $487万
 $25,244/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -34960,7 +34960,7 @@
           <t>K | 194呎 (开放式)
 $491万
 $25,322/呎
-(20年-08月-02日)</t>
+(20年-08月-03日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -34968,7 +34968,7 @@
           <t>L | 197呎 (开放式)
 $516万
 $26,182/呎
-(20年-05月-23日)</t>
+(20年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -34983,7 +34983,7 @@
           <t>A | 258呎 (1房)
 $604万
 $23,401/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -34991,7 +34991,7 @@
           <t>B | 413呎 (2房)
 $1042万
 $25,232/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -34999,7 +34999,7 @@
           <t>C | 248呎 (1房)
 $596万
 $24,030/呎
-(20年-08月-19日)</t>
+(20年-08月-20日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -35007,7 +35007,7 @@
           <t>D | 257呎 (1房)
 $620万
 $24,115/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -35015,7 +35015,7 @@
           <t>E | 257呎 (1房)
 $643万
 $25,003/呎
-(21年-09月-02日)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -35023,7 +35023,7 @@
           <t>F | 257呎 (1房)
 $604万
 $23,496/呎
-(21年-03月-08日)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -35031,7 +35031,7 @@
           <t>G | 400呎 (2房)
 $923万
 $23,079/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -35039,7 +35039,7 @@
           <t>H | 286呎 (1房)
 $712万
 $24,913/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -35047,7 +35047,7 @@
           <t>J | 193呎 (开放式)
 $475万
 $24,609/呎
-(20年-07月-16日)</t>
+(20年-07月-17日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -35055,7 +35055,7 @@
           <t>K | 194呎 (开放式)
 $484万
 $24,954/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -35063,7 +35063,7 @@
           <t>L | 197呎 (开放式)
 $483万
 $24,507/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -35078,7 +35078,7 @@
           <t>A | 258呎 (1房)
 $599万
 $23,236/呎
-(21年-02月-22日)</t>
+(21年-02月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -35086,7 +35086,7 @@
           <t>B | 413呎 (2房)
 $991万
 $24,005/呎
-(23年-01月-25日)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -35094,7 +35094,7 @@
           <t>C | 248呎 (1房)
 $598万
 $24,106/呎
-(20年-09月-08日)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -35102,7 +35102,7 @@
           <t>D | 257呎 (1房)
 $622万
 $24,199/呎
-(21年-04月-19日)</t>
+(21年-04月-20日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -35110,7 +35110,7 @@
           <t>E | 257呎 (1房)
 $638万
 $24,822/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -35118,7 +35118,7 @@
           <t>F | 257呎 (1房)
 $606万
 $23,580/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -35126,7 +35126,7 @@
           <t>G | 400呎 (2房)
 $916万
 $22,910/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -35134,7 +35134,7 @@
           <t>H | 286呎 (1房)
 $676万
 $23,638/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -35142,7 +35142,7 @@
           <t>J | 193呎 (开放式)
 $476万
 $24,688/呎
-(20年-07月-16日)</t>
+(20年-07月-17日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -35150,7 +35150,7 @@
           <t>K | 194呎 (开放式)
 $475万
 $24,506/呎
-(20年-06月-18日)</t>
+(20年-06月-19日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -35158,7 +35158,7 @@
           <t>L | 197呎 (开放式)
 $505万
 $25,619/呎
-(20年-06月-14日)</t>
+(20年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -35173,7 +35173,7 @@
           <t>A | 258呎 (1房)
 $597万
 $23,153/呎
-(21年-01月-22日)</t>
+(21年-01月-23日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -35181,7 +35181,7 @@
           <t>B | 413呎 (2房)
 $977万
 $23,655/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -35189,7 +35189,7 @@
           <t>C | 248呎 (1房)
 $596万
 $24,015/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -35197,7 +35197,7 @@
           <t>D | 257呎 (1房)
 $620万
 $24,111/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -35205,7 +35205,7 @@
           <t>E | 257呎 (1房)
 $636万
 $24,733/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -35213,7 +35213,7 @@
           <t>F | 257呎 (1房)
 $604万
 $23,493/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -35221,7 +35221,7 @@
           <t>G | 399呎 (2房)
 $913万
 $22,883/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -35229,7 +35229,7 @@
           <t>H | 287呎 (1房)
 $705万
 $24,551/呎
-(21年-09月-15日)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -35237,7 +35237,7 @@
           <t>J | 193呎 (开放式)
 $475万
 $24,596/呎
-(20年-06月-16日)</t>
+(20年-06月-17日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -35245,7 +35245,7 @@
           <t>K | 194呎 (开放式)
 $479万
 $24,677/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -35253,7 +35253,7 @@
           <t>L | 197呎 (开放式)
 $472万
 $23,982/呎
-(20年-06月-15日)</t>
+(20年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -35268,7 +35268,7 @@
           <t>A | 258呎 (1房)
 $624万
 $24,173/呎
-(21年-06月-10日)</t>
+(21年-06月-11日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -35276,7 +35276,7 @@
           <t>B | 413呎 (2房)
 $980万
 $23,740/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -35284,7 +35284,7 @@
           <t>C | 247呎 (1房)
 $623万
 $25,207/呎
-(20年-09月-02日)</t>
+(20年-09月-03日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -35292,7 +35292,7 @@
           <t>D | 257呎 (1房)
 $615万
 $23,939/呎
-(21年-04月-19日)</t>
+(21年-04月-20日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -35300,7 +35300,7 @@
           <t>E | 257呎 (1房)
 $631万
 $24,552/呎
-(21年-08月-15日)</t>
+(21年-08月-16日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -35308,7 +35308,7 @@
           <t>F | 257呎 (1房)
 $615万
 $23,916/呎
-(21年-06月-14日)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -35316,7 +35316,7 @@
           <t>G | 400呎 (2房)
 $906万
 $22,656/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -35324,7 +35324,7 @@
           <t>H | 286呎 (1房)
 $668万
 $23,372/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -35332,7 +35332,7 @@
           <t>J | 193呎 (开放式)
 $471万
 $24,411/呎
-(20年-06月-22日)</t>
+(20年-06月-23日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -35340,7 +35340,7 @@
           <t>K | 194呎 (开放式)
 $470万
 $24,233/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -35348,7 +35348,7 @@
           <t>L | 197呎 (开放式)
 $474万
 $24,058/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -35363,7 +35363,7 @@
           <t>A | 258呎 (1房)
 $617万
 $23,910/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>B | 413呎 (2房)
 $971万
 $23,514/呎
-(20年-06月-11日)</t>
+(20年-06月-12日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -35379,7 +35379,7 @@
           <t>C | 248呎 (1房)
 $584万
 $23,568/呎
-(20年-08月-17日)</t>
+(20年-08月-18日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -35387,7 +35387,7 @@
           <t>D | 257呎 (1房)
 $602万
 $23,424/呎
-(21年-04月-11日)</t>
+(21年-04月-12日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -35395,7 +35395,7 @@
           <t>E | 257呎 (1房)
 $596万
 $23,192/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -35403,7 +35403,7 @@
           <t>F | 257呎 (1房)
 $614万
 $23,910/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -35411,7 +35411,7 @@
           <t>G | 399呎 (2房)
 $896万
 $22,463/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -35419,7 +35419,7 @@
           <t>H | 287呎 (1房)
 $691万
 $24,091/呎
-(21年-09月-19日)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -35427,7 +35427,7 @@
           <t>J | 193呎 (开放式)
 $461万
 $23,876/呎
-(20年-05月-28日)</t>
+(20年-05月-29日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -35435,7 +35435,7 @@
           <t>K | 194呎 (开放式)
 $465万
 $23,959/呎
-(20年-06月-22日)</t>
+(20年-06月-23日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -35443,7 +35443,7 @@
           <t>L | 197呎 (开放式)
 $469万
 $23,801/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -35458,7 +35458,7 @@
           <t>A | 237呎 (1房)
 $630万
 $26,586/呎
-(22年-08月-31日)</t>
+(22年-09月-01日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -35466,7 +35466,7 @@
           <t>B | 376呎 (2房)
 $875万
 $23,271/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -35474,7 +35474,7 @@
           <t>C | 226呎 (1房)
 $610万
 $26,991/呎
-(22年-09月-13日)</t>
+(22年-09月-14日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -35482,7 +35482,7 @@
           <t>D | 236呎 (1房)
 $630万
 $26,695/呎
-(22年-08月-23日)</t>
+(22年-08月-24日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -35490,7 +35490,7 @@
           <t>E | 236呎 (1房)
 $520万
 $22,034/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -35498,7 +35498,7 @@
           <t>F | 236呎 (1房)
 $618万
 $26,186/呎
-(22年-08月-23日)</t>
+(22年-08月-24日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -35506,7 +35506,7 @@
           <t>G | 362呎 (2房)
 $888万
 $24,530/呎
-(22年-11月-10日)</t>
+(22年-11月-11日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -35514,7 +35514,7 @@
           <t>H | 265呎 (1房)
 $698万
 $26,340/呎
-(22年-08月-22日)</t>
+(22年-08月-23日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -35522,7 +35522,7 @@
           <t>J | 171呎 (开放式)
 $510万
 $29,825/呎
-(23年-03月-09日)</t>
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -35530,7 +35530,7 @@
           <t>K | 172呎 (开放式)
 $512万
 $29,767/呎
-(22年-10月-19日)</t>
+(22年-10月-20日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -35538,7 +35538,7 @@
           <t>L | 174呎 (开放式)
 $490万
 $28,161/呎
-(22年-10月-10日)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-旺角-利奥坊．曦岸.xlsx
+++ b/files/九龙-旺角-利奥坊．曦岸.xlsx
@@ -122,8 +122,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -268,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17992,11 +17991,11 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -18006,12 +18005,12 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J281" s="3" t="inlineStr">
@@ -18021,12 +18020,12 @@
       </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
@@ -18036,7 +18035,7 @@
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33591,27 +33590,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -33685,10 +33684,10 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 687呎 (3房)
-招标单位
+          <t>A | 697呎 (3房)
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">

--- a/files/九龙-旺角-利奥坊．曦岸.xlsx
+++ b/files/九龙-旺角-利奥坊．曦岸.xlsx
@@ -122,7 +122,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -267,7 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17995,7 +17996,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -18005,12 +18006,12 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J281" s="3" t="inlineStr">
@@ -18020,12 +18021,12 @@
       </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
@@ -18035,7 +18036,7 @@
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33590,27 +33591,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -33685,9 +33686,9 @@
       <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 697呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
